--- a/data/artifact-records-template.xlsx
+++ b/data/artifact-records-template.xlsx
@@ -1,47 +1,730 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\20260831_camel\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF8C003-8873-45AD-BBBC-0252132BBC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="records" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="171">
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>record_url</t>
+  </si>
+  <si>
+    <t>image_path</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>rights</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>loulan-la</t>
+  </si>
+  <si>
+    <t>String of 25 glass beads of different shapes and colours</t>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/6D85CEDE6B2E4733B2517DE77B53DB20/</t>
+  </si>
+  <si>
+    <t>International Dunhuang Project (IDP)</t>
+  </si>
+  <si>
+    <t>public_domain</t>
+  </si>
+  <si>
+    <t>ready</t>
+  </si>
+  <si>
+    <t>images/artifacts/loulan-glass-beads.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/loulan_basket.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/loulan_Lamp made of clay.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/A25AF3B62E6049ED925BFBCD4A1F5D66/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/6D181214CC2A458FADDEAE6136B8F6F4/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lamp made of clay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/0D4245613C8C4842B3EFBCA0ADE5DFA3/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Small wooden comb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A shoe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/loulan_shoe.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/loulan_Small wooden comb.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/8D6A6F5BDD934B85A23FE881BFC63EDB/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.britishmuseum.org/collection/object/A_MAS-710</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cupboard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The British Museum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佛塔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.britishmuseum.org/collection/object/A_MAS-706</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Male face with a caduceus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://zh.wikipedia.org/wiki/File:Male_face_with_a_caduceus_-_Google_Art_Project.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wiki</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Xinjiang Uygur Autonomous Region Institute of Cultural Relics and Archaeology</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>半袖袍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/p/1EU6erwxjh/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Loulan tomb mural</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Loulan_Mural_Tomb_(mural).jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>site_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>miran-fort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Miran fresco</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/File:Miran_fresco_12.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stupa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Miran_BLP466_PHOTO1187_2_165.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bodhisattva</t>
+  </si>
+  <si>
+    <t>https://www.britishmuseum.org/collection/object/A_1928-1022-9?selectedImageId=1133145001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.britishmuseum.org/collection/object/A_MAS-621?selectedImageId=249099001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>armour</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.britishmuseum.org/collection/object/A_MAS-626</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Buddha_with_Six_Disciples.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Buddha </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>two women</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/Miran_(Xinjiang)#/media/File:Ladies_of_Miran.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://archive.org/details/ruinsofdesertcat01stei/page/n738/mode/1up</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUDDHIST SHRINE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ink seal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/32C8EE750DEE417BA9B9F6BE291061ED/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/62FC16D8652D4031A94F83445C1D18C1/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cotton fabric lotuses</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yumenguan-pass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Dunhuang.yumenguan.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小方盤城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yangguan-pass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陽關山塔防遺跡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Yangguan.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/loulan_cupboard.png</t>
+  </si>
+  <si>
+    <t>images/artifacts/loulan_stupa.png</t>
+  </si>
+  <si>
+    <t>images/artifacts/loulan_Male_face.jpg</t>
+  </si>
+  <si>
+    <t>images/artifacts/loulan_Mural_Tomb.jpg</t>
+  </si>
+  <si>
+    <t>images/artifacts/Miran_fresco_12.jpg</t>
+  </si>
+  <si>
+    <t>images/artifacts/Miran_BLP466_PHOTO1187_2_165.jpg</t>
+  </si>
+  <si>
+    <t>images/artifacts/miran_Bodhisattva.png</t>
+  </si>
+  <si>
+    <t>images/artifacts/miran_armour.png</t>
+  </si>
+  <si>
+    <t>images/artifacts/miran_arrow.png</t>
+  </si>
+  <si>
+    <t>images/artifacts/miran_Buddha_with_Six_Disciples.png</t>
+  </si>
+  <si>
+    <t>images/artifacts/miran_twoLadies.png</t>
+  </si>
+  <si>
+    <t>images/artifacts/miran_BUDDHIST SHRINE.jpg</t>
+  </si>
+  <si>
+    <t>images/artifacts/miran_inkseal.png</t>
+  </si>
+  <si>
+    <t>images/artifacts/miran_cotton fabric lotuses.png</t>
+  </si>
+  <si>
+    <t>images/artifacts/yumenguan_smaill.jpg</t>
+  </si>
+  <si>
+    <t>images/artifacts/Yangguan.jpg</t>
+  </si>
+  <si>
+    <t>images/artifacts/loulan_half.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>niya-nxiv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>table</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.britishmuseum.org/collection/object/A_1907-1111-85</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_table.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.britishmuseum.org/collection/object/A_MAS-535</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>panel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.britishmuseum.org/collection/object/A_MAS-556</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>figure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_figure.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.britishmuseum.org/collection/object/A_1907-1111-92?selectedImageId=9188003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_seal.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.britishmuseum.org/collection/object/A_MAS-524?selectedImageId=1141681001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>batik</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Niya_batik.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Niya_batik.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Niya site</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Niya_BLP164_PHOTO392_34_165.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Niya_BLP164_PHOTO392_34_165.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://baike.baidu.com/pic/%E5%B0%BC%E9%9B%85%E9%81%97%E5%9D%80/770953/0/728da9773912b31bb051553ec54d217adab44aed4bd4#aid=0&amp;pic=728da9773912b31bb051553ec54d217adab44aed4bd4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精絕王</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_king.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>百度百科</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_site02.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://baike.baidu.com/pic/%E5%B0%BC%E9%9B%85%E9%81%97%E5%9D%80/770953/4298920770/d058ccbf6c81800a19d8f316f26024fa828ba61ee9d4?fr=newalbum&amp;fromModule=album#aid=4298920770&amp;pic=d058ccbf6c81800a19d8f316f26024fa828ba61ee9d4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_hat01.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://baike.baidu.com/pic/%E5%B0%BC%E9%9B%85%E9%81%97%E5%9D%80/770953/4298920771/dcc451da81cb39dbb6fd2c4e93431e24ab18972b9ad4?fr=newalbum&amp;fromModule=album#aid=4298920771&amp;pic=dcc451da81cb39dbb6fd2c4e93431e24ab18972b9ad4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Niya hat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_hat02.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://baike.baidu.com/pic/%E5%B0%BC%E9%9B%85%E9%81%97%E5%9D%80/770953/4298920771/dcc451da81cb39dbb6fd2c4e93431e24ab18972b9ad4?fr=newalbum&amp;fromModule=album#aid=4298920771&amp;pic=80cb39dbb6fd5266d016890ce84d802bd40735fa98d4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_dress01.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://baike.baidu.com/pic/%E5%B0%BC%E9%9B%85%E9%81%97%E5%9D%80/770953/4298920771/dcc451da81cb39dbb6fd2c4e93431e24ab18972b9ad4?fr=newalbum&amp;fromModule=album#aid=4298920771&amp;pic=38dbb6fd5266d01609242a30d47ec30735fae6cd9fd4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃袍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_dress02.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://baike.baidu.com/pic/%E5%B0%BC%E9%9B%85%E9%81%97%E5%9D%80/770953/4298920771/dcc451da81cb39dbb6fd2c4e93431e24ab18972b9ad4?fr=newalbum&amp;fromModule=album#aid=4298920771&amp;pic=5366d0160924ab18972b572f76aff1cd7b899e519dd4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠袍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_people.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://wapbaike.baidu.com/tashuo/browse/content?id=a243ebc29b54f92066d6c7a2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精絕貴族</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_5star.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精絕五星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_house.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尼雅房子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Endere_Stupa.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Endere_Stupa_BLP467_PHOTO1187_2_172.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endere-fort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stupa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Endere_dice.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.britishmuseum.org/collection/object/A_1907-1111-144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Endere_Pillars.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Endere_BLP209_PHOTO392_26_197.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pillars</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/yotkan_figurine.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/4D36D9C04BC04AEF89AF9B8C2DB385CE/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>figurine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khotan-yotkan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/yotkan_Khotan_king.JPG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Portrait_of_a_Khotan_king.JPG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>King</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yoktan clay figure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/08D98152DCDA46E3884648F25E01DE2D/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>International Dunhuang Project (IDP)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Yoktan clay figure.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rawak-stupa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Rawak_Temple_01.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Rawak_Temple_01.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Rawak_BLP170_PHOTO392_26_154.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/File:Rawak_BLP170_PHOTO392_26_154.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/yotkan_figurine02.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/009F1328AF40461DBB5BA9E013D9568D/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Yotkan_boar.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/233655BF4FCA43AA88D07E188599591B/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Yotkan_lionface.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/6D61CB1337B840D1AD67454C080901EC/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lion's face</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Yotkan_camel.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/D65E6A4E7F05427B897E28AD7A79F675/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>camel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/4CD6724FD10B4650BEEB14EA6C81ACBE/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monkey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Yotkan_monkey01.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/Yotkan_monkey02.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://idp.bl.uk/collection/4CA0178BB51E41C696EC85C460CFD896/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_panel.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/artifacts/niya_chair.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -61,17 +744,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,67 +1091,1297 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="58.83203125" customWidth="1"/>
-    <col min="3" max="3" width="68.83203125" customWidth="1"/>
-    <col min="4" max="4" width="46.83203125" customWidth="1"/>
-    <col min="5" max="5" width="38.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" customWidth="1"/>
+    <col min="3" max="3" width="49.7265625" customWidth="1"/>
+    <col min="4" max="4" width="31.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.1796875" customWidth="1"/>
+    <col min="6" max="6" width="20.81640625" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>site_id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>title</v>
-      </c>
-      <c r="C1" t="str">
-        <v>record_url</v>
-      </c>
-      <c r="D1" t="str">
-        <v>image_path</v>
-      </c>
-      <c r="E1" t="str">
-        <v>source</v>
-      </c>
-      <c r="F1" t="str">
-        <v>rights</v>
-      </c>
-      <c r="G1" t="str">
-        <v>status</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>loulan-la</v>
-      </c>
-      <c r="B2" t="str">
-        <v>String of 25 glass beads of different shapes and colours</v>
-      </c>
-      <c r="C2" t="str">
-        <v>https://idp.bl.uk/collection/6D85CEDE6B2E4733B2517DE77B53DB20/</v>
-      </c>
-      <c r="D2" t="str">
-        <v>images/artifacts/loulan-glass-beads.png</v>
-      </c>
-      <c r="E2" t="str">
-        <v>International Dunhuang Project (IDP)</v>
-      </c>
-      <c r="F2" t="str">
-        <v>public_domain</v>
-      </c>
-      <c r="G2" t="str">
-        <v>ready</v>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" t="s">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" t="s">
+        <v>170</v>
+      </c>
+      <c r="E27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" t="s">
+        <v>106</v>
+      </c>
+      <c r="F33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" t="s">
+        <v>117</v>
+      </c>
+      <c r="E36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" t="s">
+        <v>120</v>
+      </c>
+      <c r="E37" t="s">
+        <v>106</v>
+      </c>
+      <c r="F37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" t="s">
+        <v>123</v>
+      </c>
+      <c r="E38" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" t="s">
+        <v>125</v>
+      </c>
+      <c r="E39" t="s">
+        <v>106</v>
+      </c>
+      <c r="F39" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D40" t="s">
+        <v>127</v>
+      </c>
+      <c r="E40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D41" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42" t="s">
+        <v>134</v>
+      </c>
+      <c r="E42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D43" t="s">
+        <v>137</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E44" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D45" t="s">
+        <v>147</v>
+      </c>
+      <c r="E45" t="s">
+        <v>146</v>
+      </c>
+      <c r="F45" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" t="s">
+        <v>151</v>
+      </c>
+      <c r="E47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>140</v>
+      </c>
+      <c r="B48" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D48" t="s">
+        <v>153</v>
+      </c>
+      <c r="E48" t="s">
+        <v>146</v>
+      </c>
+      <c r="F48" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B49" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D49" t="s">
+        <v>155</v>
+      </c>
+      <c r="E49" t="s">
+        <v>146</v>
+      </c>
+      <c r="F49" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50" t="s">
+        <v>160</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D50" t="s">
+        <v>158</v>
+      </c>
+      <c r="E50" t="s">
+        <v>146</v>
+      </c>
+      <c r="F50" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" t="s">
+        <v>163</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D51" t="s">
+        <v>161</v>
+      </c>
+      <c r="E51" t="s">
+        <v>146</v>
+      </c>
+      <c r="F51" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>140</v>
+      </c>
+      <c r="B52" t="s">
+        <v>165</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D52" t="s">
+        <v>166</v>
+      </c>
+      <c r="E52" t="s">
+        <v>146</v>
+      </c>
+      <c r="F52" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" t="s">
+        <v>165</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D53" t="s">
+        <v>167</v>
+      </c>
+      <c r="E53" t="s">
+        <v>146</v>
+      </c>
+      <c r="F53" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{E3BEE4E4-8ED5-4206-BD2B-20A9424FD545}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{841572AE-5099-44BD-A917-45729862EBE8}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{C96636F3-4ECD-4E87-BEA6-03624ED30C6F}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{9BAC95F7-8061-45B2-A487-66576DA29365}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{56260899-46B1-48D3-A3DA-5133C27EB96E}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{DE17BE86-D071-48DD-BB18-4977B2131A90}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{07790A63-A796-4F7F-BAD0-5F1A43A9DF28}"/>
+    <hyperlink ref="C10" r:id="rId8" xr:uid="{61518161-F26F-4C0B-B735-8D4A73E843E9}"/>
+    <hyperlink ref="C11" r:id="rId9" xr:uid="{89F54314-21EB-4C81-8E8F-C1104CA0A13F}"/>
+    <hyperlink ref="C12" r:id="rId10" xr:uid="{62B8F721-2877-44A1-A3A1-99B03D7E90E7}"/>
+    <hyperlink ref="C13" r:id="rId11" xr:uid="{7D65092B-240D-4FCA-A15E-0C97BF64B5FB}"/>
+    <hyperlink ref="C14" r:id="rId12" xr:uid="{8B8F4CD9-4915-4DBB-B8E5-25084246CDC6}"/>
+    <hyperlink ref="C15" r:id="rId13" xr:uid="{89CF4C4C-4519-4944-A26D-CF479A433547}"/>
+    <hyperlink ref="C16" r:id="rId14" xr:uid="{701287B6-EA59-4BF9-AFC2-755659B32FDD}"/>
+    <hyperlink ref="C17" r:id="rId15" xr:uid="{3A0AE228-A3FF-4C21-8421-6B3CFB63B9A8}"/>
+    <hyperlink ref="C18" r:id="rId16" location="/media/File:Ladies_of_Miran.png" xr:uid="{F59E663D-ADEE-4B86-9387-C0C035B76823}"/>
+    <hyperlink ref="C19" r:id="rId17" xr:uid="{EFFF1083-C1B8-4027-8248-74B0982DD8BC}"/>
+    <hyperlink ref="C20" r:id="rId18" xr:uid="{3AEEFA49-EDB5-46F7-A6A1-16BF6C3E3920}"/>
+    <hyperlink ref="C21" r:id="rId19" xr:uid="{3AA79CAF-5B01-4DDD-80D4-9B724E24D8FA}"/>
+    <hyperlink ref="C22" r:id="rId20" xr:uid="{2ED48C8F-63E5-47DF-B912-71D672B075B2}"/>
+    <hyperlink ref="C23" r:id="rId21" xr:uid="{241FC431-9EF8-492A-8982-E908C1C29EC4}"/>
+    <hyperlink ref="C24" r:id="rId22" xr:uid="{73446860-A1D3-4357-A90A-99717A5B7031}"/>
+    <hyperlink ref="C25" r:id="rId23" xr:uid="{5E871518-A24D-4B16-B1E9-E4060AC93A0A}"/>
+    <hyperlink ref="C26" r:id="rId24" xr:uid="{E3E197F1-9BB9-4685-A093-EB9F90AFD114}"/>
+    <hyperlink ref="C27" r:id="rId25" xr:uid="{06591E39-D3FD-4C9A-B688-66E8B61BB968}"/>
+    <hyperlink ref="C28" r:id="rId26" xr:uid="{21AA2C43-E8C8-4643-81F1-249CD8460D45}"/>
+    <hyperlink ref="C29" r:id="rId27" xr:uid="{342578BB-975E-4EE7-B4B8-95EF8D8073FA}"/>
+    <hyperlink ref="C30" r:id="rId28" xr:uid="{9655CAAC-5EE0-4BAD-8F04-E81085704914}"/>
+    <hyperlink ref="C31" r:id="rId29" location="aid=0&amp;pic=728da9773912b31bb051553ec54d217adab44aed4bd4" xr:uid="{051D706D-3A23-40C1-857B-869C382046E0}"/>
+    <hyperlink ref="C32" r:id="rId30" location="aid=4298920770&amp;pic=d058ccbf6c81800a19d8f316f26024fa828ba61ee9d4" xr:uid="{6C064DBB-C56E-4812-A441-CE98B7D6E700}"/>
+    <hyperlink ref="C33" r:id="rId31" location="aid=4298920771&amp;pic=dcc451da81cb39dbb6fd2c4e93431e24ab18972b9ad4" xr:uid="{7C434B19-1064-4E02-BBA5-B889E50E4A58}"/>
+    <hyperlink ref="C34" r:id="rId32" location="aid=4298920771&amp;pic=80cb39dbb6fd5266d016890ce84d802bd40735fa98d4" xr:uid="{7B99A581-1BE0-47FD-BE9C-857C124C1392}"/>
+    <hyperlink ref="C35" r:id="rId33" location="aid=4298920771&amp;pic=38dbb6fd5266d01609242a30d47ec30735fae6cd9fd4" xr:uid="{7237F30C-113A-4539-9C49-46BA66256B11}"/>
+    <hyperlink ref="C36" r:id="rId34" location="aid=4298920771&amp;pic=5366d0160924ab18972b572f76aff1cd7b899e519dd4" xr:uid="{12016964-8A2D-4B27-8F7B-56E35B970552}"/>
+    <hyperlink ref="C37" r:id="rId35" xr:uid="{EB86DC57-F4F0-4979-92A6-679296F9741C}"/>
+    <hyperlink ref="C38" r:id="rId36" xr:uid="{E7B8DD54-21FD-40C9-8D33-7A24C4AB1B7C}"/>
+    <hyperlink ref="C39" r:id="rId37" xr:uid="{415ED620-F788-41DF-8369-D7A26172ABE7}"/>
+    <hyperlink ref="C40" r:id="rId38" xr:uid="{4A053BAC-5A60-4EFA-87CD-BC5D476277C1}"/>
+    <hyperlink ref="C41" r:id="rId39" xr:uid="{DE9186B1-D379-44B8-85EB-755B031B1951}"/>
+    <hyperlink ref="C42" r:id="rId40" xr:uid="{CDCD4280-7555-4283-B70C-EBDD32B7F52D}"/>
+    <hyperlink ref="C43" r:id="rId41" xr:uid="{EBD2E5C8-0646-4273-AD94-8B662F06E3EE}"/>
+    <hyperlink ref="C44" r:id="rId42" xr:uid="{1EE46F5B-641D-4BF4-B423-58E6FC74AC8F}"/>
+    <hyperlink ref="C45" r:id="rId43" xr:uid="{35506699-BD04-4497-8984-9CD64CC48B32}"/>
+    <hyperlink ref="C46" r:id="rId44" xr:uid="{44129C73-1535-4BAA-832E-7790213C880D}"/>
+    <hyperlink ref="C47" r:id="rId45" xr:uid="{8319E34C-3E29-4C99-B778-CE1C9E89F3AC}"/>
+    <hyperlink ref="C48" r:id="rId46" xr:uid="{845E8F24-9FA0-4DCA-A22B-E771B24FDD0A}"/>
+    <hyperlink ref="C49" r:id="rId47" xr:uid="{3F31F1D5-E244-4E5B-B489-9258868FFF8B}"/>
+    <hyperlink ref="C50" r:id="rId48" xr:uid="{B0F43EF7-1BDC-45A6-A306-9AC8F57EE074}"/>
+    <hyperlink ref="C51" r:id="rId49" xr:uid="{B9D21729-1FEA-4505-8EAA-5523892A980C}"/>
+    <hyperlink ref="C52" r:id="rId50" xr:uid="{B73EE050-9AF0-45B7-AE1A-81D601B43775}"/>
+    <hyperlink ref="C53" r:id="rId51" xr:uid="{9116DCD0-CBBC-4A8E-B282-158452CD3791}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId52"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError sqref="B1:G1 A2:C2 E2:G2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>